--- a/src/main/resources/excel_data/UserUpload.xlsx
+++ b/src/main/resources/excel_data/UserUpload.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ostan/Documents/Automation/ctp-contiplus-web-qa-automation-java/src/main/resources/excel_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishmitha G\Documents\Automation\ctp-contiplus-web-qa-automation-java\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B40CB73-38C4-2443-A080-DC33B215D045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF5E76A-FC6D-4AEB-904A-33F378504FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Fullname</t>
   </si>
@@ -43,34 +56,28 @@
     <t>testUser1@mail.com</t>
   </si>
   <si>
+    <t>Customer Template</t>
+  </si>
+  <si>
+    <t>Bulk Upload 2</t>
+  </si>
+  <si>
+    <t>bulkimport2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Bulk Upload 1</t>
+  </si>
+  <si>
+    <t>bulkimport1@maildrop.cc</t>
+  </si>
+  <si>
     <t>+919234567890</t>
   </si>
   <si>
-    <t>Customer Template</t>
-  </si>
-  <si>
-    <t>Bulk Upload 1</t>
-  </si>
-  <si>
-    <t>Bulk Upload 2</t>
-  </si>
-  <si>
-    <t>bulkimport1@maildrop.cc</t>
-  </si>
-  <si>
-    <t>bulkimport2@maildrop.cc</t>
-  </si>
-  <si>
-    <t>pp</t>
-  </si>
-  <si>
-    <t>Template Name</t>
-  </si>
-  <si>
-    <t>TestNewTemp</t>
-  </si>
-  <si>
-    <t>Templates1</t>
+    <t>vtesttemp1</t>
+  </si>
+  <si>
+    <t>2customTemplate</t>
   </si>
 </sst>
 </file>
@@ -86,16 +93,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -120,12 +128,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -441,87 +459,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.59765625" customWidth="1"/>
     <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>4</v>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{31361282-B49C-4C44-97C2-B86EE4453273}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{F977BBDB-B7BA-5249-8FEA-1C84670240D6}"/>
+    <hyperlink ref="B3" r:id="rId1" tooltip="mailto:bulkimport1@maildrop.cc" display="mailto:bulkimport1@maildrop.cc" xr:uid="{DC88CA7C-CD27-48B1-B67D-4C12548A20F8}"/>
+    <hyperlink ref="B4" r:id="rId2" tooltip="mailto:bulkimport2@maildrop.cc" display="mailto:bulkimport2@maildrop.cc" xr:uid="{51E1DBFA-B220-4CA5-BF0D-BBB3D5ACDD28}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/excel_data/UserUpload.xlsx
+++ b/src/main/resources/excel_data/UserUpload.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishmitha G\Documents\Automation\ctp-contiplus-web-qa-automation-java\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF5E76A-FC6D-4AEB-904A-33F378504FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACB7C9D-C87F-4419-B229-6ECE38BC7023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>Fullname</t>
   </si>
@@ -74,10 +74,7 @@
     <t>+919234567890</t>
   </si>
   <si>
-    <t>vtesttemp1</t>
-  </si>
-  <si>
-    <t>2customTemplate</t>
+    <t>uploadcustomTemplate</t>
   </si>
 </sst>
 </file>
@@ -163,9 +160,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,7 +200,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -309,7 +306,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -451,7 +448,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -516,7 +513,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -533,7 +530,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
